--- a/VerveStacks_EGY_grids_kan10/vt_vervestacks_EGY_v1.xlsx
+++ b/VerveStacks_EGY_grids_kan10/vt_vervestacks_EGY_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EGY_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58A5C9F6-5410-49B8-9982-FEC3FE87E499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62DD94C9-874B-4BA4-83FF-2E969E862A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{16A95A75-70C7-4029-9492-545206A6FC3F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{887E6CEF-5C68-4999-AE57-E99207DC9970}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2551,7 +2551,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{123509E1-7C8D-4290-B04F-E7C32F6B5ADD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D0A40F5-EFE4-4DC7-B6CE-0002902D64CD}">
   <dimension ref="B9:V127"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9885,7 +9885,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B199BC6-F6CB-43A4-BACB-1421BC9A6A73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D3DBA2-2AD5-480B-BB4F-D577782A5357}">
   <dimension ref="B9:W55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12752,7 +12752,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6EAE754-2770-4C0B-8677-C849EF63379C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C7908BB-610B-443D-87F8-7ECBF3ABB156}">
   <dimension ref="B9:W207"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20812,7 +20812,7 @@
         <v>15</v>
       </c>
       <c r="S145" t="s">
-        <v>368</v>
+        <v>238</v>
       </c>
       <c r="T145" t="s">
         <v>231</v>
@@ -20874,7 +20874,7 @@
         <v>15</v>
       </c>
       <c r="S146" t="s">
-        <v>238</v>
+        <v>368</v>
       </c>
       <c r="T146" t="s">
         <v>231</v>
@@ -23960,7 +23960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930FD6A4-D83D-4E56-8F5D-D76D41EB6570}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCCD8D84-B266-4FA0-BD52-F63F9C110229}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
